--- a/artfynd/A 19444-2026 artfynd.xlsx
+++ b/artfynd/A 19444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118172573</v>
+        <v>118172574</v>
       </c>
       <c r="B2" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512595</v>
+        <v>512599</v>
       </c>
       <c r="R2" t="n">
-        <v>7006523</v>
+        <v>7006530</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118172575</v>
+        <v>118172579</v>
       </c>
       <c r="B3" t="n">
-        <v>97745</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512588</v>
+        <v>512543</v>
       </c>
       <c r="R3" t="n">
-        <v>7006546</v>
+        <v>7006444</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118172581</v>
+        <v>118172576</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512501</v>
+        <v>512583</v>
       </c>
       <c r="R4" t="n">
-        <v>7006459</v>
+        <v>7006568</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118172576</v>
+        <v>118172581</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512583</v>
+        <v>512501</v>
       </c>
       <c r="R5" t="n">
-        <v>7006568</v>
+        <v>7006459</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118172577</v>
+        <v>118172578</v>
       </c>
       <c r="B6" t="n">
-        <v>97869</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512571</v>
+        <v>512597</v>
       </c>
       <c r="R6" t="n">
-        <v>7006560</v>
+        <v>7006523</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118172582</v>
+        <v>118172575</v>
       </c>
       <c r="B7" t="n">
-        <v>97750</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220093</v>
+        <v>219795</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512570</v>
+        <v>512588</v>
       </c>
       <c r="R7" t="n">
-        <v>7006565</v>
+        <v>7006546</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118172574</v>
+        <v>118172577</v>
       </c>
       <c r="B8" t="n">
-        <v>74588</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512599</v>
+        <v>512571</v>
       </c>
       <c r="R8" t="n">
-        <v>7006530</v>
+        <v>7006560</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118172579</v>
+        <v>118172582</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512543</v>
+        <v>512570</v>
       </c>
       <c r="R9" t="n">
-        <v>7006444</v>
+        <v>7006565</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118172578</v>
+        <v>118172572</v>
       </c>
       <c r="B10" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512597</v>
+        <v>512614</v>
       </c>
       <c r="R10" t="n">
-        <v>7006523</v>
+        <v>7006530</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1590,6 +1545,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118172573</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ramsmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512595</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7006523</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19444-2026 artfynd.xlsx
+++ b/artfynd/A 19444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172576</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172581</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172578</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172577</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172572</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172573</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>